--- a/artfynd/A 30693-2022 artfynd.xlsx
+++ b/artfynd/A 30693-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30693-2022 artfynd.xlsx
+++ b/artfynd/A 30693-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,61 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109543870</v>
+        <v>107257805</v>
       </c>
       <c r="B2" t="n">
-        <v>57064</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103055</v>
+        <v>100137</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Slaguggla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Strix uralensis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Pallas, 1771</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Jägarmossen, Upl</t>
+          <t>Rörsbyvägen, Norrtälje 1315 m N, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>680271.2992091893</v>
+        <v>680289</v>
       </c>
       <c r="R2" t="n">
-        <v>6634944.967359118</v>
+        <v>6634941</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,22 +756,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-03-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>02:41</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-27</t>
+          <t>2023-03-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>02:41</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,65 +786,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Ulf Elman</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ulf Elman</t>
+          <t>Tobias Ljungquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119137217</v>
+        <v>109543870</v>
       </c>
       <c r="B3" t="n">
-        <v>104915</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221141</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mälsättra, Upl</t>
+          <t>Jägarmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>680285</v>
+        <v>680271</v>
       </c>
       <c r="R3" t="n">
-        <v>6634931</v>
+        <v>6634945</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>02:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-29</t>
+          <t>2023-05-27</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>02:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,15 +899,112 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Ulf Elman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Ulf Elman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119137217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106156</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221141</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gullviva</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Primula veris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Mälsättra, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>680285</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6634931</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Fasterna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Karin Agstam-Norlin</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Karin Agstam-Norlin</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 30693-2022 artfynd.xlsx
+++ b/artfynd/A 30693-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107257805</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109543870</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1009,8 +1024,18 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119137217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>